--- a/PythonScripts/Chili_Produkt_Fűszerkereskedelmi_Korlátolt_Felelősségű_Társaság_Beszamolo_Elemzes.xlsx
+++ b/PythonScripts/Chili_Produkt_Fűszerkereskedelmi_Korlátolt_Felelősségű_Társaság_Beszamolo_Elemzes.xlsx
@@ -1348,34 +1348,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52</v>
+        <v>172</v>
       </c>
       <c r="C26" t="n">
-        <v>53</v>
+        <v>173</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="E26" t="n">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="F26" t="n">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="G26" t="n">
-        <v>57</v>
+        <v>177</v>
       </c>
       <c r="H26" t="n">
-        <v>58</v>
+        <v>178</v>
       </c>
       <c r="I26" t="n">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="J26" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="K26" t="n">
-        <v>61</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27">
@@ -7304,7 +7304,9 @@
           <t>MUTATO: Vagyon változása (%)</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
       <c r="C187" t="n">
         <v>28.83723964704539</v>
       </c>
